--- a/data/trans_camb/P2A_fisi_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 7,8</t>
+          <t>-3,98; 6,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 5,79</t>
+          <t>-4,71; 5,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 11,54</t>
+          <t>-1,34; 11,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 5,68</t>
+          <t>-6,6; 5,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 7,55</t>
+          <t>-5,84; 7,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 11,42</t>
+          <t>-2,08; 11,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 4,94</t>
+          <t>-3,51; 4,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 4,51</t>
+          <t>-3,86; 4,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 9,45</t>
+          <t>-0,72; 9,08</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-72,35; —</t>
+          <t>-58,29; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-90,22; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,68; 1278,77</t>
+          <t>-58,17; 1025,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-70,62; 391,02</t>
+          <t>-70,2; 346,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-83,13; 348,38</t>
+          <t>-81,46; 321,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-22,97; 630,69</t>
+          <t>-28,12; 610,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,92</t>
+          <t>-0,93; 3,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,58</t>
+          <t>-1,78; 1,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 6,18</t>
+          <t>1,53; 6,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,76</t>
+          <t>-0,86; 3,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 1,14</t>
+          <t>-2,82; 1,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 6,72</t>
+          <t>1,24; 7,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,73</t>
+          <t>-0,33; 2,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 0,89</t>
+          <t>-1,86; 0,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,84</t>
+          <t>1,98; 5,73</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-46,83; 256,63</t>
+          <t>-38,99; 318,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-64,28; 136,38</t>
+          <t>-64,46; 136,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,34; 553,31</t>
+          <t>35,09; 481,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,75; 192,04</t>
+          <t>-23,91; 170,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,74; 62,41</t>
+          <t>-69,79; 60,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,22; 311,38</t>
+          <t>21,55; 322,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 148,44</t>
+          <t>-13,35; 151,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,66; 54,73</t>
+          <t>-55,74; 52,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58,94; 311,14</t>
+          <t>58,21; 295,15</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 3,07</t>
+          <t>-1,42; 3,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 7,57</t>
+          <t>0,32; 7,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 4,05</t>
+          <t>-0,58; 3,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 0,04</t>
+          <t>-7,1; -0,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,94; -0,06</t>
+          <t>-7,66; 0,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 2,47</t>
+          <t>-5,48; 2,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 0,83</t>
+          <t>-3,21; 0,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,92</t>
+          <t>-2,13; 2,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,46</t>
+          <t>-1,92; 2,5</t>
         </is>
       </c>
     </row>
@@ -1220,42 +1220,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,61; —</t>
+          <t>-44,92; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-65,0; —</t>
+          <t>-56,57; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 18,19</t>
+          <t>-100,0; 50,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 22,94</t>
+          <t>-100,0; 43,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-84,77; 138,44</t>
+          <t>-82,29; 146,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-85,98; 87,3</t>
+          <t>-88,92; 69,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-56,18; 203,6</t>
+          <t>-63,29; 198,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-56,49; 170,85</t>
+          <t>-54,7; 167,19</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,63</t>
+          <t>-0,48; 2,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,38</t>
+          <t>-0,54; 2,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,16</t>
+          <t>1,58; 5,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 2,01</t>
+          <t>-1,6; 2,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 0,43</t>
+          <t>-2,81; 0,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,89</t>
+          <t>0,5; 4,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,79</t>
+          <t>-0,67; 1,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,91</t>
+          <t>-1,29; 0,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,49</t>
+          <t>1,63; 4,54</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-27,65; 226,97</t>
+          <t>-23,61; 226,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-30,98; 213,54</t>
+          <t>-22,92; 227,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61,99; 451,75</t>
+          <t>58,93; 440,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-36,62; 83,57</t>
+          <t>-38,18; 78,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-64,85; 20,28</t>
+          <t>-65,35; 21,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,16; 184,63</t>
+          <t>8,32; 192,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 85,41</t>
+          <t>-21,31; 86,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-40,84; 44,8</t>
+          <t>-41,62; 48,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>50,58; 209,94</t>
+          <t>46,11; 219,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_fisi_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 6,98</t>
+          <t>-4,06; 7,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 5,95</t>
+          <t>-4,79; 5,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 11,61</t>
+          <t>-2,94; 10,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 5,45</t>
+          <t>-6,41; 5,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 7,45</t>
+          <t>-6,56; 7,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 11,8</t>
+          <t>-2,99; 11,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 4,86</t>
+          <t>-3,29; 5,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 4,71</t>
+          <t>-3,71; 4,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 9,08</t>
+          <t>-0,41; 9,47</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-58,29; —</t>
+          <t>-78,89; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-90,22; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-58,17; 1025,77</t>
+          <t>-63,65; 929,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-70,2; 346,59</t>
+          <t>-66,44; 384,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-81,46; 321,46</t>
+          <t>-79,51; 412,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-28,12; 610,8</t>
+          <t>-19,3; 677,1</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,13</t>
+          <t>-1,06; 3,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,58</t>
+          <t>-1,83; 1,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 6,12</t>
+          <t>1,67; 6,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 3,76</t>
+          <t>-0,85; 3,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 1,0</t>
+          <t>-2,75; 1,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 7,13</t>
+          <t>1,35; 7,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,83</t>
+          <t>-0,4; 2,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,82</t>
+          <t>-1,71; 0,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,73</t>
+          <t>2,13; 5,79</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,99; 318,68</t>
+          <t>-41,55; 292,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-64,46; 136,29</t>
+          <t>-64,12; 163,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,09; 481,9</t>
+          <t>39,94; 588,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,91; 170,35</t>
+          <t>-22,69; 198,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,79; 60,75</t>
+          <t>-65,99; 66,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,55; 322,91</t>
+          <t>23,63; 331,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 151,18</t>
+          <t>-12,8; 151,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,74; 52,47</t>
+          <t>-53,91; 50,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58,21; 295,15</t>
+          <t>61,21; 317,43</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 3,29</t>
+          <t>-1,39; 3,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 7,28</t>
+          <t>0,61; 7,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 3,93</t>
+          <t>-0,71; 3,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,1; -0,07</t>
+          <t>-6,82; 0,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 0,12</t>
+          <t>-6,58; 0,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 2,61</t>
+          <t>-5,31; 2,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,77</t>
+          <t>-3,44; 0,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,66</t>
+          <t>-1,88; 2,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,5</t>
+          <t>-2,0; 2,43</t>
         </is>
       </c>
     </row>
@@ -1220,42 +1220,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-44,92; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-56,57; —</t>
+          <t>-73,89; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 50,03</t>
+          <t>-100,0; 68,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 43,36</t>
+          <t>-93,25; 48,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-82,29; 146,74</t>
+          <t>-80,65; 118,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-88,92; 69,18</t>
+          <t>-89,92; 66,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-63,29; 198,38</t>
+          <t>-52,65; 207,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-54,7; 167,19</t>
+          <t>-54,77; 175,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,69</t>
+          <t>-0,43; 2,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 2,43</t>
+          <t>-0,57; 2,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,08</t>
+          <t>1,73; 5,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,02</t>
+          <t>-1,73; 2,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 0,42</t>
+          <t>-2,96; 0,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,98</t>
+          <t>0,62; 5,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,69</t>
+          <t>-0,58; 1,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,97</t>
+          <t>-1,33; 0,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,54</t>
+          <t>1,72; 4,5</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-23,61; 226,94</t>
+          <t>-21,71; 250,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 227,7</t>
+          <t>-27,8; 207,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58,93; 440,23</t>
+          <t>55,04; 443,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-38,18; 78,49</t>
+          <t>-41,21; 81,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-65,35; 21,11</t>
+          <t>-67,88; 22,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,32; 192,01</t>
+          <t>12,54; 202,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,31; 86,76</t>
+          <t>-18,64; 97,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-41,62; 48,6</t>
+          <t>-41,2; 46,21</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>46,11; 219,88</t>
+          <t>52,12; 215,08</t>
         </is>
       </c>
     </row>
